--- a/Documents/MMO_Project_Design_Data_Tracker.xlsx
+++ b/Documents/MMO_Project_Design_Data_Tracker.xlsx
@@ -1234,7 +1234,7 @@
       </c>
       <c r="B4" s="30" t="inlineStr">
         <is>
-          <t>Save / persistence system</t>
+          <t>Fixed: Save / persistence system implemented (see Feature Checklist)</t>
         </is>
       </c>
       <c r="C4" s="30" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="B6" s="30" t="inlineStr">
         <is>
-          <t>Skill buffs / debuffs (temporary stat modifiers)</t>
+          <t>Fixed: Skill buffs / debuffs implemented (BuffController, see Feature Checklist)</t>
         </is>
       </c>
       <c r="C6" s="30" t="inlineStr">
@@ -1294,7 +1294,7 @@
       </c>
       <c r="B8" s="30" t="inlineStr">
         <is>
-          <t>Elemental damage and enemy resistances</t>
+          <t>Fixed: Elemental damage and enemy resistances implemented (see Feature Checklist)</t>
         </is>
       </c>
       <c r="C8" s="30" t="inlineStr">
@@ -1354,7 +1354,7 @@
       </c>
       <c r="B12" s="30" t="inlineStr">
         <is>
-          <t>Ammo item type</t>
+          <t>Fixed: Ammo item type implemented (see Feature Checklist)</t>
         </is>
       </c>
       <c r="C12" s="30" t="inlineStr">
@@ -1406,7 +1406,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:D59"/>
+  <dimension ref="A1:D64"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="18" customWidth="1" style="25" min="1" max="1"/>
@@ -1588,12 +1588,12 @@
       </c>
       <c r="C14" s="39" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="D14" s="30" t="inlineStr">
         <is>
-          <t>Depends on weapon/class systems not built yet</t>
+          <t>AttackSpeedCalculator + CharacterStatsDefinition.BaseAttackSpeed, AGI/DEX-scaled per real RO formula</t>
         </is>
       </c>
     </row>
@@ -1628,12 +1628,12 @@
       </c>
       <c r="C16" s="39" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="D16" s="30" t="inlineStr">
         <is>
-          <t>Placeholder: flat 1 point per increase</t>
+          <t>RagnarokStatPointCostStrategy: floor((X-1)/10)+2, real iRO Wiki Classic curve</t>
         </is>
       </c>
     </row>
@@ -1802,12 +1802,12 @@
       </c>
       <c r="C25" s="39" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="D25" s="30" t="inlineStr">
         <is>
-          <t>Attacks currently always connect</t>
+          <t>HitChanceCalculator.RollHit: 100+(Hit-Flee)%, clamped 5-95%</t>
         </is>
       </c>
     </row>
@@ -1865,7 +1865,7 @@
       </c>
       <c r="D28" s="30" t="inlineStr">
         <is>
-          <t>Damage (Physical/Magical) and Heal effects, class-restricted, hotbar-cast</t>
+          <t>Damage (Physical/Magical), Heal, and Passive effect types, class-restricted, hotbar-cast, gated by a per-skill minimum Base Level requirement (2026-09-18)</t>
         </is>
       </c>
     </row>
@@ -1882,12 +1882,12 @@
       </c>
       <c r="C29" s="39" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="D29" s="30" t="inlineStr">
         <is>
-          <t>See Roadmap sheet for architecture notes</t>
+          <t>BuffController: temporary ATK/ASPD/DEF/MDEF/incoming-damage/Max HP modifiers (Berserk, Provoke, Endure, Energy Coat)</t>
         </is>
       </c>
     </row>
@@ -1926,12 +1926,12 @@
       </c>
       <c r="C31" s="39" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="D31" s="30" t="inlineStr">
         <is>
-          <t>Fire/Ice/Holy/Dark/Wind/Electric etc.</t>
+          <t>Element enum (incl. Neutral as a real resistable element) + ElementalResistanceComponent (IDamageModifier hook), wired to Poring/Poporing</t>
         </is>
       </c>
     </row>
@@ -1988,12 +1988,12 @@
       </c>
       <c r="C34" s="39" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="D34" s="30" t="inlineStr">
         <is>
-          <t>Needs stack-while-equipped handling</t>
+          <t>AmmoCounterUI + Archer ammo consumption on basic attack</t>
         </is>
       </c>
     </row>
@@ -2332,12 +2332,12 @@
       </c>
       <c r="C52" s="39" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="D52" s="30" t="inlineStr">
         <is>
-          <t>Largest known gap</t>
+          <t>ISaveParticipant/JsonFileSaveRepository — covers progression, class, skills, hotbar, inventory, equipment, window layout (GDD 8.2a)</t>
         </is>
       </c>
     </row>
@@ -2376,10 +2376,14 @@
       </c>
       <c r="C54" s="39" t="inlineStr">
         <is>
-          <t>Planned</t>
-        </is>
-      </c>
-      <c r="D54" s="30" t="n"/>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="D54" s="30" t="inlineStr">
+        <is>
+          <t>EditMode tests exist for Character Stats and Items (CharacterBaseStatsTests, EquipmentManagerTests, InventoryTests); no PlayMode test infrastructure yet</t>
+        </is>
+      </c>
     </row>
     <row r="55" ht="23.25" customHeight="1" s="26">
       <c r="A55" s="30" t="inlineStr">
@@ -2434,12 +2438,12 @@
       </c>
       <c r="C57" s="39" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="D57" s="30" t="inlineStr">
         <is>
-          <t>See Quasi-Stats sheet</t>
+          <t>Attack Range, Weight Limit, Movement Speed and Status Effect Resistance implemented; Cast Time/Cast Delay/Critical Hit Shield/Perfect Dodge/Perfect Hit still planned — see Quasi-Stats sheet</t>
         </is>
       </c>
     </row>
@@ -2456,12 +2460,12 @@
       </c>
       <c r="C58" s="39" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="D58" s="30" t="inlineStr">
         <is>
-          <t>No reset mechanism exists yet</t>
+          <t>CharacterBaseStats.ResetToMinimum()/PlayerStatsController.ResetStats() implemented, but deliberately kept out of the shipped UI (debug-menu-only) per Victor’s 2026-09-08 decision</t>
         </is>
       </c>
     </row>
@@ -2484,6 +2488,116 @@
       <c r="D59" s="30" t="inlineStr">
         <is>
           <t>Assumes 4th-job content far beyond current roadmap</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Combat</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Status effect system (Stun, Poison, Silence, Blind, Freeze, Petrify)</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>StatusEffectController, wired to Fatal Blow (stun-augment) and SkillDefinition.InflictedStatus</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Combat</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Status effect resistance</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>See Quasi-Stats sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Character Stats</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Monster Size/Race classification + weapon-vs-size damage table</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>WeaponSizeModifiers, real iRO Wiki Classic size table; wired on Poring (Small/Plant) and Poporing</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Character Stats</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Class-specific Job Level stat bonuses</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>ClassJobLevelBonusLookup, e.g. Swordman +7 STR/+2 AGI/+4 VIT/+3 DEX/+2 LUK at Job 50</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Combat</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Natural HP regeneration</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>PlayerHealthRegenController, boosted by Increase HP Recovery / HP Recovery While Moving passives</t>
         </is>
       </c>
     </row>
@@ -8619,7 +8733,7 @@
       </c>
       <c r="C14" s="30" t="inlineStr">
         <is>
-          <t>Planned — no status effect system exists yet</t>
+          <t>Implemented 2026-09-23 — VIT-derived for the player ((VIT+3)/100, clamped), flat CharacterStatsDefinition.StatusResistChance per enemy. One unified roll for all six statuses, not per-status VIT/LUK split (see FUTURE_IMPROVEMENTS.md).</t>
         </is>
       </c>
     </row>
@@ -12645,827 +12759,827 @@
       </c>
     </row>
     <row r="418">
-      <c r="A418" t="inlineStr">
+      <c r="A418" s="25" t="inlineStr">
         <is>
           <t>Base EXP Required per Level (implemented 2026-09-18)</t>
         </is>
       </c>
     </row>
     <row r="419">
-      <c r="A419" t="inlineStr">
+      <c r="A419" s="25" t="inlineStr">
         <is>
           <t>Source: iRO Wiki Classic — Base EXP Chart (irowiki.org/classic/Base_EXP_Chart), consulted September 2026. No closed-form formula exists in the real game for this curve, unlike the stat-point curves above — this is an authored table, hardcoded as a lookup array in RealRagnarokExperienceCurve.cs (Project.Character.Combat), replacing the old LinearExperienceCurve placeholder.</t>
         </is>
       </c>
     </row>
     <row r="420">
-      <c r="A420" t="inlineStr">
+      <c r="A420" s="25" t="inlineStr">
         <is>
           <t>Level 99 requires no further EXP — this project's current level cap (no rebirth/transcendence exists here), matching the wiki's own "maxed" entry.</t>
         </is>
       </c>
     </row>
     <row r="422">
-      <c r="A422" t="inlineStr">
+      <c r="A422" s="25" t="inlineStr">
         <is>
           <t>Level</t>
         </is>
       </c>
-      <c r="B422" t="inlineStr">
+      <c r="B422" s="25" t="inlineStr">
         <is>
           <t>EXP to Next Level</t>
         </is>
       </c>
     </row>
     <row r="423">
-      <c r="A423" t="n">
+      <c r="A423" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="B423" t="n">
+      <c r="B423" s="25" t="n">
         <v>9</v>
       </c>
     </row>
     <row r="424">
-      <c r="A424" t="n">
+      <c r="A424" s="25" t="n">
         <v>2</v>
       </c>
-      <c r="B424" t="n">
+      <c r="B424" s="25" t="n">
         <v>16</v>
       </c>
     </row>
     <row r="425">
-      <c r="A425" t="n">
+      <c r="A425" s="25" t="n">
         <v>3</v>
       </c>
-      <c r="B425" t="n">
+      <c r="B425" s="25" t="n">
         <v>25</v>
       </c>
     </row>
     <row r="426">
-      <c r="A426" t="n">
+      <c r="A426" s="25" t="n">
         <v>4</v>
       </c>
-      <c r="B426" t="n">
+      <c r="B426" s="25" t="n">
         <v>36</v>
       </c>
     </row>
     <row r="427">
-      <c r="A427" t="n">
+      <c r="A427" s="25" t="n">
         <v>5</v>
       </c>
-      <c r="B427" t="n">
+      <c r="B427" s="25" t="n">
         <v>77</v>
       </c>
     </row>
     <row r="428">
-      <c r="A428" t="n">
+      <c r="A428" s="25" t="n">
         <v>6</v>
       </c>
-      <c r="B428" t="n">
+      <c r="B428" s="25" t="n">
         <v>112</v>
       </c>
     </row>
     <row r="429">
-      <c r="A429" t="n">
+      <c r="A429" s="25" t="n">
         <v>7</v>
       </c>
-      <c r="B429" t="n">
+      <c r="B429" s="25" t="n">
         <v>153</v>
       </c>
     </row>
     <row r="430">
-      <c r="A430" t="n">
+      <c r="A430" s="25" t="n">
         <v>8</v>
       </c>
-      <c r="B430" t="n">
+      <c r="B430" s="25" t="n">
         <v>200</v>
       </c>
     </row>
     <row r="431">
-      <c r="A431" t="n">
+      <c r="A431" s="25" t="n">
         <v>9</v>
       </c>
-      <c r="B431" t="n">
+      <c r="B431" s="25" t="n">
         <v>253</v>
       </c>
     </row>
     <row r="432">
-      <c r="A432" t="n">
+      <c r="A432" s="25" t="n">
         <v>10</v>
       </c>
-      <c r="B432" t="n">
+      <c r="B432" s="25" t="n">
         <v>320</v>
       </c>
     </row>
     <row r="433">
-      <c r="A433" t="n">
+      <c r="A433" s="25" t="n">
         <v>11</v>
       </c>
-      <c r="B433" t="n">
+      <c r="B433" s="25" t="n">
         <v>385</v>
       </c>
     </row>
     <row r="434">
-      <c r="A434" t="n">
+      <c r="A434" s="25" t="n">
         <v>12</v>
       </c>
-      <c r="B434" t="n">
+      <c r="B434" s="25" t="n">
         <v>490</v>
       </c>
     </row>
     <row r="435">
-      <c r="A435" t="n">
+      <c r="A435" s="25" t="n">
         <v>13</v>
       </c>
-      <c r="B435" t="n">
+      <c r="B435" s="25" t="n">
         <v>585</v>
       </c>
     </row>
     <row r="436">
-      <c r="A436" t="n">
+      <c r="A436" s="25" t="n">
         <v>14</v>
       </c>
-      <c r="B436" t="n">
+      <c r="B436" s="25" t="n">
         <v>700</v>
       </c>
     </row>
     <row r="437">
-      <c r="A437" t="n">
+      <c r="A437" s="25" t="n">
         <v>15</v>
       </c>
-      <c r="B437" t="n">
+      <c r="B437" s="25" t="n">
         <v>830</v>
       </c>
     </row>
     <row r="438">
-      <c r="A438" t="n">
+      <c r="A438" s="25" t="n">
         <v>16</v>
       </c>
-      <c r="B438" t="n">
+      <c r="B438" s="25" t="n">
         <v>970</v>
       </c>
     </row>
     <row r="439">
-      <c r="A439" t="n">
+      <c r="A439" s="25" t="n">
         <v>17</v>
       </c>
-      <c r="B439" t="n">
+      <c r="B439" s="25" t="n">
         <v>1120</v>
       </c>
     </row>
     <row r="440">
-      <c r="A440" t="n">
+      <c r="A440" s="25" t="n">
         <v>18</v>
       </c>
-      <c r="B440" t="n">
+      <c r="B440" s="25" t="n">
         <v>1260</v>
       </c>
     </row>
     <row r="441">
-      <c r="A441" t="n">
+      <c r="A441" s="25" t="n">
         <v>19</v>
       </c>
-      <c r="B441" t="n">
+      <c r="B441" s="25" t="n">
         <v>1420</v>
       </c>
     </row>
     <row r="442">
-      <c r="A442" t="n">
+      <c r="A442" s="25" t="n">
         <v>20</v>
       </c>
-      <c r="B442" t="n">
+      <c r="B442" s="25" t="n">
         <v>1620</v>
       </c>
     </row>
     <row r="443">
-      <c r="A443" t="n">
+      <c r="A443" s="25" t="n">
         <v>21</v>
       </c>
-      <c r="B443" t="n">
+      <c r="B443" s="25" t="n">
         <v>1860</v>
       </c>
     </row>
     <row r="444">
-      <c r="A444" t="n">
+      <c r="A444" s="25" t="n">
         <v>22</v>
       </c>
-      <c r="B444" t="n">
+      <c r="B444" s="25" t="n">
         <v>1990</v>
       </c>
     </row>
     <row r="445">
-      <c r="A445" t="n">
+      <c r="A445" s="25" t="n">
         <v>23</v>
       </c>
-      <c r="B445" t="n">
+      <c r="B445" s="25" t="n">
         <v>2240</v>
       </c>
     </row>
     <row r="446">
-      <c r="A446" t="n">
+      <c r="A446" s="25" t="n">
         <v>24</v>
       </c>
-      <c r="B446" t="n">
+      <c r="B446" s="25" t="n">
         <v>2504</v>
       </c>
     </row>
     <row r="447">
-      <c r="A447" t="n">
+      <c r="A447" s="25" t="n">
         <v>25</v>
       </c>
-      <c r="B447" t="n">
+      <c r="B447" s="25" t="n">
         <v>2950</v>
       </c>
     </row>
     <row r="448">
-      <c r="A448" t="n">
+      <c r="A448" s="25" t="n">
         <v>26</v>
       </c>
-      <c r="B448" t="n">
+      <c r="B448" s="25" t="n">
         <v>3426</v>
       </c>
     </row>
     <row r="449">
-      <c r="A449" t="n">
+      <c r="A449" s="25" t="n">
         <v>27</v>
       </c>
-      <c r="B449" t="n">
+      <c r="B449" s="25" t="n">
         <v>3934</v>
       </c>
     </row>
     <row r="450">
-      <c r="A450" t="n">
+      <c r="A450" s="25" t="n">
         <v>28</v>
       </c>
-      <c r="B450" t="n">
+      <c r="B450" s="25" t="n">
         <v>4474</v>
       </c>
     </row>
     <row r="451">
-      <c r="A451" t="n">
+      <c r="A451" s="25" t="n">
         <v>29</v>
       </c>
-      <c r="B451" t="n">
+      <c r="B451" s="25" t="n">
         <v>6889</v>
       </c>
     </row>
     <row r="452">
-      <c r="A452" t="n">
+      <c r="A452" s="25" t="n">
         <v>30</v>
       </c>
-      <c r="B452" t="n">
+      <c r="B452" s="25" t="n">
         <v>7995</v>
       </c>
     </row>
     <row r="453">
-      <c r="A453" t="n">
+      <c r="A453" s="25" t="n">
         <v>31</v>
       </c>
-      <c r="B453" t="n">
+      <c r="B453" s="25" t="n">
         <v>9174</v>
       </c>
     </row>
     <row r="454">
-      <c r="A454" t="n">
+      <c r="A454" s="25" t="n">
         <v>32</v>
       </c>
-      <c r="B454" t="n">
+      <c r="B454" s="25" t="n">
         <v>10425</v>
       </c>
     </row>
     <row r="455">
-      <c r="A455" t="n">
+      <c r="A455" s="25" t="n">
         <v>33</v>
       </c>
-      <c r="B455" t="n">
+      <c r="B455" s="25" t="n">
         <v>11748</v>
       </c>
     </row>
     <row r="456">
-      <c r="A456" t="n">
+      <c r="A456" s="25" t="n">
         <v>34</v>
       </c>
-      <c r="B456" t="n">
+      <c r="B456" s="25" t="n">
         <v>13967</v>
       </c>
     </row>
     <row r="457">
-      <c r="A457" t="n">
+      <c r="A457" s="25" t="n">
         <v>35</v>
       </c>
-      <c r="B457" t="n">
+      <c r="B457" s="25" t="n">
         <v>15775</v>
       </c>
     </row>
     <row r="458">
-      <c r="A458" t="n">
+      <c r="A458" s="25" t="n">
         <v>36</v>
       </c>
-      <c r="B458" t="n">
+      <c r="B458" s="25" t="n">
         <v>17678</v>
       </c>
     </row>
     <row r="459">
-      <c r="A459" t="n">
+      <c r="A459" s="25" t="n">
         <v>37</v>
       </c>
-      <c r="B459" t="n">
+      <c r="B459" s="25" t="n">
         <v>19677</v>
       </c>
     </row>
     <row r="460">
-      <c r="A460" t="n">
+      <c r="A460" s="25" t="n">
         <v>38</v>
       </c>
-      <c r="B460" t="n">
+      <c r="B460" s="25" t="n">
         <v>21773</v>
       </c>
     </row>
     <row r="461">
-      <c r="A461" t="n">
+      <c r="A461" s="25" t="n">
         <v>39</v>
       </c>
-      <c r="B461" t="n">
+      <c r="B461" s="25" t="n">
         <v>30543</v>
       </c>
     </row>
     <row r="462">
-      <c r="A462" t="n">
+      <c r="A462" s="25" t="n">
         <v>40</v>
       </c>
-      <c r="B462" t="n">
+      <c r="B462" s="25" t="n">
         <v>34212</v>
       </c>
     </row>
     <row r="463">
-      <c r="A463" t="n">
+      <c r="A463" s="25" t="n">
         <v>41</v>
       </c>
-      <c r="B463" t="n">
+      <c r="B463" s="25" t="n">
         <v>38065</v>
       </c>
     </row>
     <row r="464">
-      <c r="A464" t="n">
+      <c r="A464" s="25" t="n">
         <v>42</v>
       </c>
-      <c r="B464" t="n">
+      <c r="B464" s="25" t="n">
         <v>42102</v>
       </c>
     </row>
     <row r="465">
-      <c r="A465" t="n">
+      <c r="A465" s="25" t="n">
         <v>43</v>
       </c>
-      <c r="B465" t="n">
+      <c r="B465" s="25" t="n">
         <v>46323</v>
       </c>
     </row>
     <row r="466">
-      <c r="A466" t="n">
+      <c r="A466" s="25" t="n">
         <v>44</v>
       </c>
-      <c r="B466" t="n">
+      <c r="B466" s="25" t="n">
         <v>53026</v>
       </c>
     </row>
     <row r="467">
-      <c r="A467" t="n">
+      <c r="A467" s="25" t="n">
         <v>45</v>
       </c>
-      <c r="B467" t="n">
+      <c r="B467" s="25" t="n">
         <v>58419</v>
       </c>
     </row>
     <row r="468">
-      <c r="A468" t="n">
+      <c r="A468" s="25" t="n">
         <v>46</v>
       </c>
-      <c r="B468" t="n">
+      <c r="B468" s="25" t="n">
         <v>64041</v>
       </c>
     </row>
     <row r="469">
-      <c r="A469" t="n">
+      <c r="A469" s="25" t="n">
         <v>47</v>
       </c>
-      <c r="B469" t="n">
+      <c r="B469" s="25" t="n">
         <v>69892</v>
       </c>
     </row>
     <row r="470">
-      <c r="A470" t="n">
+      <c r="A470" s="25" t="n">
         <v>48</v>
       </c>
-      <c r="B470" t="n">
+      <c r="B470" s="25" t="n">
         <v>75973</v>
       </c>
     </row>
     <row r="471">
-      <c r="A471" t="n">
+      <c r="A471" s="25" t="n">
         <v>49</v>
       </c>
-      <c r="B471" t="n">
+      <c r="B471" s="25" t="n">
         <v>102468</v>
       </c>
     </row>
     <row r="472">
-      <c r="A472" t="n">
+      <c r="A472" s="25" t="n">
         <v>50</v>
       </c>
-      <c r="B472" t="n">
+      <c r="B472" s="25" t="n">
         <v>115254</v>
       </c>
     </row>
     <row r="473">
-      <c r="A473" t="n">
+      <c r="A473" s="25" t="n">
         <v>51</v>
       </c>
-      <c r="B473" t="n">
+      <c r="B473" s="25" t="n">
         <v>128692</v>
       </c>
     </row>
     <row r="474">
-      <c r="A474" t="n">
+      <c r="A474" s="25" t="n">
         <v>52</v>
       </c>
-      <c r="B474" t="n">
+      <c r="B474" s="25" t="n">
         <v>142784</v>
       </c>
     </row>
     <row r="475">
-      <c r="A475" t="n">
+      <c r="A475" s="25" t="n">
         <v>53</v>
       </c>
-      <c r="B475" t="n">
+      <c r="B475" s="25" t="n">
         <v>157528</v>
       </c>
     </row>
     <row r="476">
-      <c r="A476" t="n">
+      <c r="A476" s="25" t="n">
         <v>54</v>
       </c>
-      <c r="B476" t="n">
+      <c r="B476" s="25" t="n">
         <v>178184</v>
       </c>
     </row>
     <row r="477">
-      <c r="A477" t="n">
+      <c r="A477" s="25" t="n">
         <v>55</v>
       </c>
-      <c r="B477" t="n">
+      <c r="B477" s="25" t="n">
         <v>196300</v>
       </c>
     </row>
     <row r="478">
-      <c r="A478" t="n">
+      <c r="A478" s="25" t="n">
         <v>56</v>
       </c>
-      <c r="B478" t="n">
+      <c r="B478" s="25" t="n">
         <v>215198</v>
       </c>
     </row>
     <row r="479">
-      <c r="A479" t="n">
+      <c r="A479" s="25" t="n">
         <v>57</v>
       </c>
-      <c r="B479" t="n">
+      <c r="B479" s="25" t="n">
         <v>234879</v>
       </c>
     </row>
     <row r="480">
-      <c r="A480" t="n">
+      <c r="A480" s="25" t="n">
         <v>58</v>
       </c>
-      <c r="B480" t="n">
+      <c r="B480" s="25" t="n">
         <v>255341</v>
       </c>
     </row>
     <row r="481">
-      <c r="A481" t="n">
+      <c r="A481" s="25" t="n">
         <v>59</v>
       </c>
-      <c r="B481" t="n">
+      <c r="B481" s="25" t="n">
         <v>330188</v>
       </c>
     </row>
     <row r="482">
-      <c r="A482" t="n">
+      <c r="A482" s="25" t="n">
         <v>60</v>
       </c>
-      <c r="B482" t="n">
+      <c r="B482" s="25" t="n">
         <v>365914</v>
       </c>
     </row>
     <row r="483">
-      <c r="A483" t="n">
+      <c r="A483" s="25" t="n">
         <v>61</v>
       </c>
-      <c r="B483" t="n">
+      <c r="B483" s="25" t="n">
         <v>403224</v>
       </c>
     </row>
     <row r="484">
-      <c r="A484" t="n">
+      <c r="A484" s="25" t="n">
         <v>62</v>
       </c>
-      <c r="B484" t="n">
+      <c r="B484" s="25" t="n">
         <v>442116</v>
       </c>
     </row>
     <row r="485">
-      <c r="A485" t="n">
+      <c r="A485" s="25" t="n">
         <v>63</v>
       </c>
-      <c r="B485" t="n">
+      <c r="B485" s="25" t="n">
         <v>482590</v>
       </c>
     </row>
     <row r="486">
-      <c r="A486" t="n">
+      <c r="A486" s="25" t="n">
         <v>64</v>
       </c>
-      <c r="B486" t="n">
+      <c r="B486" s="25" t="n">
         <v>536948</v>
       </c>
     </row>
     <row r="487">
-      <c r="A487" t="n">
+      <c r="A487" s="25" t="n">
         <v>65</v>
       </c>
-      <c r="B487" t="n">
+      <c r="B487" s="25" t="n">
         <v>585191</v>
       </c>
     </row>
     <row r="488">
-      <c r="A488" t="n">
+      <c r="A488" s="25" t="n">
         <v>66</v>
       </c>
-      <c r="B488" t="n">
+      <c r="B488" s="25" t="n">
         <v>635278</v>
       </c>
     </row>
     <row r="489">
-      <c r="A489" t="n">
+      <c r="A489" s="25" t="n">
         <v>67</v>
       </c>
-      <c r="B489" t="n">
+      <c r="B489" s="25" t="n">
         <v>687211</v>
       </c>
     </row>
     <row r="490">
-      <c r="A490" t="n">
+      <c r="A490" s="25" t="n">
         <v>68</v>
       </c>
-      <c r="B490" t="n">
+      <c r="B490" s="25" t="n">
         <v>740988</v>
       </c>
     </row>
     <row r="491">
-      <c r="A491" t="n">
+      <c r="A491" s="25" t="n">
         <v>69</v>
       </c>
-      <c r="B491" t="n">
+      <c r="B491" s="25" t="n">
         <v>925400</v>
       </c>
     </row>
     <row r="492">
-      <c r="A492" t="n">
+      <c r="A492" s="25" t="n">
         <v>70</v>
       </c>
-      <c r="B492" t="n">
+      <c r="B492" s="25" t="n">
         <v>1473746</v>
       </c>
     </row>
     <row r="493">
-      <c r="A493" t="n">
+      <c r="A493" s="25" t="n">
         <v>71</v>
       </c>
-      <c r="B493" t="n">
+      <c r="B493" s="25" t="n">
         <v>1594058</v>
       </c>
     </row>
     <row r="494">
-      <c r="A494" t="n">
+      <c r="A494" s="25" t="n">
         <v>72</v>
       </c>
-      <c r="B494" t="n">
+      <c r="B494" s="25" t="n">
         <v>1718928</v>
       </c>
     </row>
     <row r="495">
-      <c r="A495" t="n">
+      <c r="A495" s="25" t="n">
         <v>73</v>
       </c>
-      <c r="B495" t="n">
+      <c r="B495" s="25" t="n">
         <v>1848355</v>
       </c>
     </row>
     <row r="496">
-      <c r="A496" t="n">
+      <c r="A496" s="25" t="n">
         <v>74</v>
       </c>
-      <c r="B496" t="n">
+      <c r="B496" s="25" t="n">
         <v>1982340</v>
       </c>
     </row>
     <row r="497">
-      <c r="A497" t="n">
+      <c r="A497" s="25" t="n">
         <v>75</v>
       </c>
-      <c r="B497" t="n">
+      <c r="B497" s="25" t="n">
         <v>2230113</v>
       </c>
     </row>
     <row r="498">
-      <c r="A498" t="n">
+      <c r="A498" s="25" t="n">
         <v>76</v>
       </c>
-      <c r="B498" t="n">
+      <c r="B498" s="25" t="n">
         <v>2386162</v>
       </c>
     </row>
     <row r="499">
-      <c r="A499" t="n">
+      <c r="A499" s="25" t="n">
         <v>77</v>
       </c>
-      <c r="B499" t="n">
+      <c r="B499" s="25" t="n">
         <v>2547417</v>
       </c>
     </row>
     <row r="500">
-      <c r="A500" t="n">
+      <c r="A500" s="25" t="n">
         <v>78</v>
       </c>
-      <c r="B500" t="n">
+      <c r="B500" s="25" t="n">
         <v>2713878</v>
       </c>
     </row>
     <row r="501">
-      <c r="A501" t="n">
+      <c r="A501" s="25" t="n">
         <v>79</v>
       </c>
-      <c r="B501" t="n">
+      <c r="B501" s="25" t="n">
         <v>3206160</v>
       </c>
     </row>
     <row r="502">
-      <c r="A502" t="n">
+      <c r="A502" s="25" t="n">
         <v>80</v>
       </c>
-      <c r="B502" t="n">
+      <c r="B502" s="25" t="n">
         <v>3681024</v>
       </c>
     </row>
     <row r="503">
-      <c r="A503" t="n">
+      <c r="A503" s="25" t="n">
         <v>81</v>
       </c>
-      <c r="B503" t="n">
+      <c r="B503" s="25" t="n">
         <v>4022472</v>
       </c>
     </row>
     <row r="504">
-      <c r="A504" t="n">
+      <c r="A504" s="25" t="n">
         <v>82</v>
       </c>
-      <c r="B504" t="n">
+      <c r="B504" s="25" t="n">
         <v>4377024</v>
       </c>
     </row>
     <row r="505">
-      <c r="A505" t="n">
+      <c r="A505" s="25" t="n">
         <v>83</v>
       </c>
-      <c r="B505" t="n">
+      <c r="B505" s="25" t="n">
         <v>4744680</v>
       </c>
     </row>
     <row r="506">
-      <c r="A506" t="n">
+      <c r="A506" s="25" t="n">
         <v>84</v>
       </c>
-      <c r="B506" t="n">
+      <c r="B506" s="25" t="n">
         <v>5125440</v>
       </c>
     </row>
     <row r="507">
-      <c r="A507" t="n">
+      <c r="A507" s="25" t="n">
         <v>85</v>
       </c>
-      <c r="B507" t="n">
+      <c r="B507" s="25" t="n">
         <v>5767272</v>
       </c>
     </row>
     <row r="508">
-      <c r="A508" t="n">
+      <c r="A508" s="25" t="n">
         <v>86</v>
       </c>
-      <c r="B508" t="n">
+      <c r="B508" s="25" t="n">
         <v>6204000</v>
       </c>
     </row>
     <row r="509">
-      <c r="A509" t="n">
+      <c r="A509" s="25" t="n">
         <v>87</v>
       </c>
-      <c r="B509" t="n">
+      <c r="B509" s="25" t="n">
         <v>6655464</v>
       </c>
     </row>
     <row r="510">
-      <c r="A510" t="n">
+      <c r="A510" s="25" t="n">
         <v>88</v>
       </c>
-      <c r="B510" t="n">
+      <c r="B510" s="25" t="n">
         <v>7121664</v>
       </c>
     </row>
     <row r="511">
-      <c r="A511" t="n">
+      <c r="A511" s="25" t="n">
         <v>89</v>
       </c>
-      <c r="B511" t="n">
+      <c r="B511" s="25" t="n">
         <v>7602600</v>
       </c>
     </row>
     <row r="512">
-      <c r="A512" t="n">
+      <c r="A512" s="25" t="n">
         <v>90</v>
       </c>
-      <c r="B512" t="n">
+      <c r="B512" s="25" t="n">
         <v>9738720</v>
       </c>
     </row>
     <row r="513">
-      <c r="A513" t="n">
+      <c r="A513" s="25" t="n">
         <v>91</v>
       </c>
-      <c r="B513" t="n">
+      <c r="B513" s="25" t="n">
         <v>11649960</v>
       </c>
     </row>
     <row r="514">
-      <c r="A514" t="n">
+      <c r="A514" s="25" t="n">
         <v>92</v>
       </c>
-      <c r="B514" t="n">
+      <c r="B514" s="25" t="n">
         <v>13643520</v>
       </c>
     </row>
     <row r="515">
-      <c r="A515" t="n">
+      <c r="A515" s="25" t="n">
         <v>93</v>
       </c>
-      <c r="B515" t="n">
+      <c r="B515" s="25" t="n">
         <v>18339300</v>
       </c>
     </row>
     <row r="516">
-      <c r="A516" t="n">
+      <c r="A516" s="25" t="n">
         <v>94</v>
       </c>
-      <c r="B516" t="n">
+      <c r="B516" s="25" t="n">
         <v>23836800</v>
       </c>
     </row>
     <row r="517">
-      <c r="A517" t="n">
+      <c r="A517" s="25" t="n">
         <v>95</v>
       </c>
-      <c r="B517" t="n">
+      <c r="B517" s="25" t="n">
         <v>35658000</v>
       </c>
     </row>
     <row r="518">
-      <c r="A518" t="n">
+      <c r="A518" s="25" t="n">
         <v>96</v>
       </c>
-      <c r="B518" t="n">
+      <c r="B518" s="25" t="n">
         <v>48687000</v>
       </c>
     </row>
     <row r="519">
-      <c r="A519" t="n">
+      <c r="A519" s="25" t="n">
         <v>97</v>
       </c>
-      <c r="B519" t="n">
+      <c r="B519" s="25" t="n">
         <v>58135000</v>
       </c>
     </row>
     <row r="520">
-      <c r="A520" t="n">
+      <c r="A520" s="25" t="n">
         <v>98</v>
       </c>
-      <c r="B520" t="n">
+      <c r="B520" s="25" t="n">
         <v>99999998</v>
       </c>
     </row>
     <row r="521">
-      <c r="A521" t="n">
+      <c r="A521" s="25" t="n">
         <v>99</v>
       </c>
-      <c r="B521" t="inlineStr">
+      <c r="B521" s="25" t="inlineStr">
         <is>
           <t>MAX (no further leveling)</t>
         </is>

--- a/Documents/MMO_Project_Design_Data_Tracker.xlsx
+++ b/Documents/MMO_Project_Design_Data_Tracker.xlsx
@@ -1406,7 +1406,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:D64"/>
+  <dimension ref="A1:D69"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="18" customWidth="1" style="25" min="1" max="1"/>
@@ -2492,112 +2492,222 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" t="inlineStr">
+      <c r="A60" s="25" t="inlineStr">
         <is>
           <t>Combat</t>
         </is>
       </c>
-      <c r="B60" t="inlineStr">
+      <c r="B60" s="25" t="inlineStr">
         <is>
           <t>Status effect system (Stun, Poison, Silence, Blind, Freeze, Petrify)</t>
         </is>
       </c>
-      <c r="C60" t="inlineStr">
+      <c r="C60" s="25" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr">
+      <c r="D60" s="25" t="inlineStr">
         <is>
           <t>StatusEffectController, wired to Fatal Blow (stun-augment) and SkillDefinition.InflictedStatus</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" t="inlineStr">
+      <c r="A61" s="25" t="inlineStr">
         <is>
           <t>Combat</t>
         </is>
       </c>
-      <c r="B61" t="inlineStr">
+      <c r="B61" s="25" t="inlineStr">
         <is>
           <t>Status effect resistance</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr">
+      <c r="C61" s="25" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr">
+      <c r="D61" s="25" t="inlineStr">
         <is>
           <t>See Quasi-Stats sheet</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" t="inlineStr">
+      <c r="A62" s="25" t="inlineStr">
         <is>
           <t>Character Stats</t>
         </is>
       </c>
-      <c r="B62" t="inlineStr">
+      <c r="B62" s="25" t="inlineStr">
         <is>
           <t>Monster Size/Race classification + weapon-vs-size damage table</t>
         </is>
       </c>
-      <c r="C62" t="inlineStr">
+      <c r="C62" s="25" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr">
+      <c r="D62" s="25" t="inlineStr">
         <is>
           <t>WeaponSizeModifiers, real iRO Wiki Classic size table; wired on Poring (Small/Plant) and Poporing</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" t="inlineStr">
+      <c r="A63" s="25" t="inlineStr">
         <is>
           <t>Character Stats</t>
         </is>
       </c>
-      <c r="B63" t="inlineStr">
+      <c r="B63" s="25" t="inlineStr">
         <is>
           <t>Class-specific Job Level stat bonuses</t>
         </is>
       </c>
-      <c r="C63" t="inlineStr">
+      <c r="C63" s="25" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr">
+      <c r="D63" s="25" t="inlineStr">
         <is>
           <t>ClassJobLevelBonusLookup, e.g. Swordman +7 STR/+2 AGI/+4 VIT/+3 DEX/+2 LUK at Job 50</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" t="inlineStr">
+      <c r="A64" s="25" t="inlineStr">
         <is>
           <t>Combat</t>
         </is>
       </c>
-      <c r="B64" t="inlineStr">
+      <c r="B64" s="25" t="inlineStr">
         <is>
           <t>Natural HP regeneration</t>
         </is>
       </c>
-      <c r="C64" t="inlineStr">
+      <c r="C64" s="25" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr">
+      <c r="D64" s="25" t="inlineStr">
         <is>
           <t>PlayerHealthRegenController, boosted by Increase HP Recovery / HP Recovery While Moving passives</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="25" t="inlineStr">
+        <is>
+          <t>Combat</t>
+        </is>
+      </c>
+      <c r="B65" s="25" t="inlineStr">
+        <is>
+          <t>Weapon own ATK added to Status ATK</t>
+        </is>
+      </c>
+      <c r="C65" s="25" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D65" s="25" t="inlineStr">
+        <is>
+          <t>ItemDefinition.weaponAttack, EquipmentManager.GetMainHandWeaponAttack; main hand only; untested in Editor</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="25" t="inlineStr">
+        <is>
+          <t>Combat</t>
+        </is>
+      </c>
+      <c r="B66" s="25" t="inlineStr">
+        <is>
+          <t>Per-weapon attack speed multiplier</t>
+        </is>
+      </c>
+      <c r="C66" s="25" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D66" s="25" t="inlineStr">
+        <is>
+          <t>ItemDefinition.attackSpeedMultiplier divides the Aspd attack interval; GiantBlade 0.8, Zweihander 0.85</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="25" t="inlineStr">
+        <is>
+          <t>Combat</t>
+        </is>
+      </c>
+      <c r="B67" s="25" t="inlineStr">
+        <is>
+          <t>Magnum Break HP cost and Fire after-effect</t>
+        </is>
+      </c>
+      <c r="C67" s="25" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D67" s="25" t="inlineStr">
+        <is>
+          <t>HP 20 to 16, 10 s of +20% Fire damage ignoring DEF (BuffPayload.FireDamagePercent, HealthComponent.TakePiercingDamage); untested in Editor</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="25" t="inlineStr">
+        <is>
+          <t>World</t>
+        </is>
+      </c>
+      <c r="B68" s="25" t="inlineStr">
+        <is>
+          <t>Point-based enemy spawn with respawn delay per monster</t>
+        </is>
+      </c>
+      <c r="C68" s="25" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D68" s="25" t="inlineStr">
+        <is>
+          <t>EnemySpawnArea: manual points, max active, 30 s default, random free point, optional boss</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="25" t="inlineStr">
+        <is>
+          <t>Progression</t>
+        </is>
+      </c>
+      <c r="B69" s="25" t="inlineStr">
+        <is>
+          <t>Experience granted through EnemyDeathEvents</t>
+        </is>
+      </c>
+      <c r="C69" s="25" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D69" s="25" t="inlineStr">
+        <is>
+          <t>EnemyDeathHandler publishes, PlayerExperience and PlayerJobProgress subscribe; Project.AI no longer references Project.Character.Combat</t>
         </is>
       </c>
     </row>
@@ -2905,7 +3015,7 @@
       </c>
       <c r="C5" s="30" t="inlineStr">
         <is>
-          <t>Weapon ATK bonus not yet modeled. The equipped weapon TYPE decides which stat scales damage, not the player's class — a Swordman with a bow scales off DEX too.</t>
+          <t>Status ATK is only the stat part. Final ATK = Status ATK + passive mastery bonus + the main-hand weapon's own ATK (ItemDefinition.weaponAttack, added 2026-10-10), then the buff multiplier. The equipped weapon TYPE decides which stat scales damage, not the player's class — a Swordman with a bow scales off DEX too. Staffs and books add no MATK yet.</t>
         </is>
       </c>
     </row>
